--- a/Excel/ai-automation-station.xlsx
+++ b/Excel/ai-automation-station.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why OpenCode Is Better Than Claude Code (It's Free!)</t>
+          <t>Why OpenCode Is Better Than Claude Code</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29831</v>
+        <v>31446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Watch Me Build A Desktop App With OpenCode!</t>
+          <t>How To Build A Desktop App With OpenCode (Step-by-Step)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12721</v>
+        <v>14977</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -523,12 +523,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C5wEcJRo_VA</t>
+          <t>iuh5E6AK6tc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Is PI Better Than OpenCode For AI Coding?</t>
+          <t>Is OpenCode Better Than Claude Code?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -537,11 +537,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5640</v>
+        <v>5694</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0:09:07</t>
+          <t>0:00:49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -553,25 +553,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iuh5E6AK6tc</t>
+          <t>0tmhsHn5B30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Is OpenCode Better Than Claude Code?</t>
+          <t>GLM 5.2 Inside OpenCode Go In Minutes!</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5012</v>
+        <v>5446</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0:00:49</t>
+          <t>0:08:44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,25 +583,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0tmhsHn5B30</t>
+          <t>GjctLLCFdVc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GLM 5.2 Inside OpenCode Go In Minutes!</t>
+          <t>Getting Started With OpenCode Go</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2964</v>
+        <v>2477</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0:08:44</t>
+          <t>0:00:51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -613,25 +613,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ud2su6XhtKw</t>
+          <t>D3nI2JACE88</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OpenCode Makes It Easy To Build SaaS Web Apps In Minutes!</t>
+          <t>OpenCode Video Editor Skill Tutorial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1534</v>
+        <v>1828</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0:09:24</t>
+          <t>0:00:56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,21 +643,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D3nI2JACE88</t>
+          <t>ARfm6a3GM8Q</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OpenCode Video Editor Skill Tutorial</t>
+          <t>Why I switched to ZCode for GLM 5.2 #ai #coding #tech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1343</v>
+        <v>1814</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -673,25 +673,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GjctLLCFdVc</t>
+          <t>ud2su6XhtKw</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Getting Started With OpenCode Go</t>
+          <t>OpenCode Makes It Easy To Build SaaS Apps In Minutes!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1114</v>
+        <v>1767</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0:00:51</t>
+          <t>0:09:24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -703,25 +703,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DiCSqbZkxRs</t>
+          <t>mmiQaVfA5e0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Building My SaaS Web App In OpenCode #opencode</t>
+          <t>GLM 5.2 Now Has An Official Desktop App!</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>929</v>
+        <v>1378</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0:00:27</t>
+          <t>0:10:24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -733,25 +733,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARfm6a3GM8Q</t>
+          <t>aI7do8iLJCk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GLM 5.2 Desktop App Tutorial</t>
+          <t>GLM 5.2 OpenCode Tutorial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>913</v>
+        <v>1319</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0:00:56</t>
+          <t>0:00:55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
